--- a/DataTables/Datas/#CampaignData-战役表.xlsx
+++ b/DataTables/Datas/#CampaignData-战役表.xlsx
@@ -4,13 +4,10 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17055" activeTab="3"/>
+    <workbookView windowHeight="17055"/>
   </bookViews>
   <sheets>
-    <sheet name="Green" sheetId="1" r:id="rId1"/>
-    <sheet name="Blue" sheetId="2" r:id="rId2"/>
-    <sheet name="Red" sheetId="3" r:id="rId3"/>
-    <sheet name="Purple" sheetId="4" r:id="rId4"/>
+    <sheet name="1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,29 +27,20 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>##var</t>
   </si>
   <si>
-    <t>id</t>
-  </si>
-  <si>
     <t>camp</t>
   </si>
   <si>
-    <t>level_num</t>
-  </si>
-  <si>
-    <t>title</t>
+    <t>show_name</t>
   </si>
   <si>
     <t>##type</t>
   </si>
   <si>
-    <t>int</t>
-  </si>
-  <si>
     <t>ECamp</t>
   </si>
   <si>
@@ -65,43 +53,34 @@
     <t>##</t>
   </si>
   <si>
-    <t>战役编号</t>
-  </si>
-  <si>
     <t>阵营</t>
   </si>
   <si>
-    <t>关卡</t>
-  </si>
-  <si>
-    <t>标题</t>
+    <t>战役名</t>
   </si>
   <si>
     <t>Green</t>
   </si>
   <si>
-    <t>关卡1</t>
-  </si>
-  <si>
-    <t>关卡2</t>
-  </si>
-  <si>
-    <t>关卡3</t>
-  </si>
-  <si>
-    <t>关卡4</t>
-  </si>
-  <si>
-    <t>关卡5</t>
+    <t>绿色战役</t>
   </si>
   <si>
     <t>Blue</t>
   </si>
   <si>
+    <t>蓝色战役</t>
+  </si>
+  <si>
     <t>Red</t>
   </si>
   <si>
+    <t>红色战役</t>
+  </si>
+  <si>
     <t>Purple</t>
+  </si>
+  <si>
+    <t>紫色战役</t>
   </si>
 </sst>
 </file>
@@ -723,13 +702,17 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
@@ -1042,10 +1025,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
+  <dimension ref="A1:D9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <sheetData>
-    <row r="1" ht="16.5" spans="1:6">
+    <row r="1" ht="16.5" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1055,586 +1038,89 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="1"/>
+    </row>
+    <row r="2" ht="16.5" spans="1:4">
+      <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="B2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1"/>
+      <c r="C2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="1"/>
     </row>
-    <row r="2" ht="16.5" spans="1:6">
-      <c r="A2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="1" t="s">
+    <row r="3" ht="16.5" spans="1:4">
+      <c r="A3" s="1" t="s">
         <v>6</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" s="1"/>
-    </row>
-    <row r="3" ht="16.5" spans="1:6">
-      <c r="A3" s="1" t="s">
-        <v>9</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
     </row>
-    <row r="4" ht="16.5" spans="1:6">
+    <row r="4" ht="16.5" spans="1:4">
       <c r="A4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="1"/>
+    </row>
+    <row r="5" ht="16.5" spans="1:4">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="C5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="D5" s="1"/>
+    </row>
+    <row r="6" ht="16.5" spans="1:4">
+      <c r="A6" s="3"/>
+      <c r="B6" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="C6" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="D6" s="3"/>
+    </row>
+    <row r="7" ht="16.5" spans="1:4">
+      <c r="A7" s="3"/>
+      <c r="B7" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F4" s="1"/>
+      <c r="C7" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" s="3"/>
     </row>
-    <row r="5" ht="16.5" spans="1:6">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1">
-        <v>1</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5" s="1">
-        <v>1</v>
-      </c>
-      <c r="E5" s="1" t="s">
+    <row r="8" ht="16.5" spans="1:4">
+      <c r="A8" s="3"/>
+      <c r="B8" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F5" s="1"/>
+      <c r="C8" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8" s="3"/>
     </row>
-    <row r="6" ht="16.5" spans="1:6">
-      <c r="A6" s="2"/>
-      <c r="B6" s="1">
-        <v>2</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D6" s="1">
-        <v>2</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F6" s="2"/>
-    </row>
-    <row r="7" ht="16.5" spans="1:6">
-      <c r="A7" s="2"/>
-      <c r="B7" s="1">
-        <v>3</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D7" s="2">
-        <v>3</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F7" s="2"/>
-    </row>
-    <row r="8" ht="16.5" spans="1:6">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2">
-        <v>4</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D8" s="2">
-        <v>4</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F8" s="2"/>
-    </row>
-    <row r="9" ht="16.5" spans="1:6">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2">
-        <v>5</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D9" s="2">
-        <v>5</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F9" s="2"/>
+    <row r="9" ht="16.5" spans="1:4">
+      <c r="A9" s="3"/>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:E9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
-  <sheetData>
-    <row r="1" ht="16.5" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" ht="16.5" spans="1:5">
-      <c r="A2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" ht="16.5" spans="1:5">
-      <c r="A3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-    </row>
-    <row r="4" ht="16.5" spans="1:5">
-      <c r="A4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" ht="16.5" spans="1:5">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1">
-        <v>101</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D5" s="1">
-        <v>1</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" ht="16.5" spans="1:5">
-      <c r="A6" s="2"/>
-      <c r="B6" s="1">
-        <v>102</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D6" s="1">
-        <v>2</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" ht="16.5" spans="1:5">
-      <c r="A7" s="2"/>
-      <c r="B7" s="1">
-        <v>103</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D7" s="2">
-        <v>3</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="8" ht="16.5" spans="1:5">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2">
-        <v>104</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D8" s="2">
-        <v>4</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="9" ht="16.5" spans="1:5">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2">
-        <v>105</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D9" s="2">
-        <v>5</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:E9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
-  <sheetData>
-    <row r="1" ht="16.5" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" ht="16.5" spans="1:5">
-      <c r="A2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" ht="16.5" spans="1:5">
-      <c r="A3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-    </row>
-    <row r="4" ht="16.5" spans="1:5">
-      <c r="A4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" ht="16.5" spans="1:5">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1">
-        <v>201</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D5" s="1">
-        <v>1</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" ht="16.5" spans="1:5">
-      <c r="A6" s="2"/>
-      <c r="B6" s="1">
-        <v>202</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D6" s="1">
-        <v>2</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" ht="16.5" spans="1:5">
-      <c r="A7" s="2"/>
-      <c r="B7" s="1">
-        <v>203</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D7" s="2">
-        <v>3</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="8" ht="16.5" spans="1:5">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2">
-        <v>204</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D8" s="2">
-        <v>4</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="9" ht="16.5" spans="1:5">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2">
-        <v>205</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D9" s="2">
-        <v>5</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:E9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
-  <sheetData>
-    <row r="1" ht="16.5" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" ht="16.5" spans="1:5">
-      <c r="A2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" ht="16.5" spans="1:5">
-      <c r="A3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-    </row>
-    <row r="4" ht="16.5" spans="1:5">
-      <c r="A4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" ht="16.5" spans="1:5">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1">
-        <v>301</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D5" s="1">
-        <v>1</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" ht="16.5" spans="1:5">
-      <c r="A6" s="2"/>
-      <c r="B6" s="1">
-        <v>302</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D6" s="1">
-        <v>2</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" ht="16.5" spans="1:5">
-      <c r="A7" s="2"/>
-      <c r="B7" s="1">
-        <v>303</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D7" s="2">
-        <v>3</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="8" ht="16.5" spans="1:5">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2">
-        <v>304</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D8" s="2">
-        <v>4</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="9" ht="16.5" spans="1:5">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2">
-        <v>305</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D9" s="2">
-        <v>5</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
 </file>